--- a/data/Terre di Pedemonte/investment_decision/Verscio_MFH_from_2015_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Verscio_MFH_from_2015_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>47.14316606877937</v>
+        <v>15.61625732760295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>6087.082301403225</v>
       </c>
       <c r="F4" t="n">
-        <v>57.06600038770581</v>
+        <v>15.25018477047972</v>
       </c>
       <c r="G4" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="H4" t="n">
-        <v>47.02253088462979</v>
+        <v>15.30909748485199</v>
       </c>
       <c r="I4" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="J4" t="n">
-        <v>57.06600038770581</v>
+        <v>14.52376845882017</v>
       </c>
       <c r="K4" t="n">
         <v>6087.082301403225</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>47.14316606877937</v>
+        <v>15.61625732760295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>6087.082301403225</v>
       </c>
       <c r="F5" t="n">
-        <v>57.06600038770581</v>
+        <v>15.25018477047972</v>
       </c>
       <c r="G5" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="H5" t="n">
-        <v>47.02253088462979</v>
+        <v>15.30909748485199</v>
       </c>
       <c r="I5" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="J5" t="n">
-        <v>57.06600038770581</v>
+        <v>14.52376845882017</v>
       </c>
       <c r="K5" t="n">
         <v>6087.082301403225</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>47.14316606877937</v>
+        <v>21.12339590465198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>6087.082301403225</v>
       </c>
       <c r="F6" t="n">
-        <v>57.06600038770581</v>
+        <v>20.72745779576117</v>
       </c>
       <c r="G6" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="H6" t="n">
-        <v>47.02253088462979</v>
+        <v>22.30442521115527</v>
       </c>
       <c r="I6" t="n">
         <v>6087.082301403225</v>
       </c>
       <c r="J6" t="n">
-        <v>57.06600038770581</v>
+        <v>20.66837892920324</v>
       </c>
       <c r="K6" t="n">
         <v>6087.082301403225</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Verscio_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Verscio_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>9.130623452104837</v>
+        <v>23.49864</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00365315808</v>
+        <v>0.001719133214117647</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00365315808</v>
+        <v>0.001719133214117647</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003606096238279741</v>
+        <v>0.001719133214117647</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00365315808</v>
+        <v>0.001719133214117647</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00365315808</v>
+        <v>0.002363808169411765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00365315808</v>
+        <v>0.002363808169411765</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003606096238279741</v>
+        <v>0.002363808169411765</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00365315808</v>
+        <v>0.002363808169411765</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235309</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235309</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004942507990588236</v>
+        <v>0.003438266428235294</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5767775818453738</v>
+        <v>0.319651332</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5621922080664906</v>
+        <v>0.319651332</v>
       </c>
       <c r="G19" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5773902558175374</v>
+        <v>0.296819094</v>
       </c>
       <c r="I19" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5632775585225928</v>
+        <v>0.296819094</v>
       </c>
       <c r="K19" t="n">
         <v>0.7671631968</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5767775818453738</v>
+        <v>0.319651332</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5621922080664906</v>
+        <v>0.319651332</v>
       </c>
       <c r="G20" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5773902558175374</v>
+        <v>0.296819094</v>
       </c>
       <c r="I20" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5632775585225928</v>
+        <v>0.296819094</v>
       </c>
       <c r="K20" t="n">
         <v>0.7671631968</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5767775818453738</v>
+        <v>0.319651332</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5621922080664906</v>
+        <v>0.319651332</v>
       </c>
       <c r="G21" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5773902558175374</v>
+        <v>0.296819094</v>
       </c>
       <c r="I21" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5632775585225928</v>
+        <v>0.296819094</v>
       </c>
       <c r="K21" t="n">
         <v>0.7671631968</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01686060615462619</v>
+        <v>0.273986856</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03144597993350934</v>
+        <v>0.273986856</v>
       </c>
       <c r="G29" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01624793218246254</v>
+        <v>0.296819094</v>
       </c>
       <c r="I29" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03036062947740725</v>
+        <v>0.296819094</v>
       </c>
       <c r="K29" t="n">
         <v>0.7671631968</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01686060615462619</v>
+        <v>0.273986856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03144597993350934</v>
+        <v>0.273986856</v>
       </c>
       <c r="G30" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01624793218246254</v>
+        <v>0.296819094</v>
       </c>
       <c r="I30" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J30" t="n">
-        <v>0.03036062947740725</v>
+        <v>0.296819094</v>
       </c>
       <c r="K30" t="n">
         <v>0.7671631968</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01686060615462619</v>
+        <v>0.273986856</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.7671631968</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03144597993350934</v>
+        <v>0.273986856</v>
       </c>
       <c r="G31" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01624793218246254</v>
+        <v>0.296819094</v>
       </c>
       <c r="I31" t="n">
         <v>0.7671631968</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03036062947740725</v>
+        <v>0.296819094</v>
       </c>
       <c r="K31" t="n">
         <v>0.7671631968</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.4089225244215864</v>
+        <v>0.4440910173979642</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4125364625243084</v>
+        <v>0.3981754910515591</v>
       </c>
       <c r="G54" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3847150930020836</v>
+        <v>0.4416401751060239</v>
       </c>
       <c r="I54" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3866407503791901</v>
+        <v>0.3972314234780687</v>
       </c>
       <c r="K54" t="n">
         <v>1.973210785383696</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4089225244215864</v>
+        <v>0.4440910173979642</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4125364625243084</v>
+        <v>0.3981754910515591</v>
       </c>
       <c r="G55" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3847150930020836</v>
+        <v>0.4416401751060239</v>
       </c>
       <c r="I55" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3866407503791901</v>
+        <v>0.3972314234780687</v>
       </c>
       <c r="K55" t="n">
         <v>1.973210785383696</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.4089225244215864</v>
+        <v>0.4440910173979642</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4125364625243084</v>
+        <v>0.3981754910515591</v>
       </c>
       <c r="G56" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3847150930020836</v>
+        <v>0.4416401751060239</v>
       </c>
       <c r="I56" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3866407503791901</v>
+        <v>0.3972314234780687</v>
       </c>
       <c r="K56" t="n">
         <v>1.973210785383696</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.4009178912533721</v>
+        <v>0.2625101234736973</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3507906672806824</v>
+        <v>0.3129067940275872</v>
       </c>
       <c r="G64" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H64" t="n">
-        <v>0.4256908000985762</v>
+        <v>0.2687209513841501</v>
       </c>
       <c r="I64" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3766863794258007</v>
+        <v>0.3227430229605531</v>
       </c>
       <c r="K64" t="n">
         <v>1.973210785383696</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.4009178912533721</v>
+        <v>0.2625101234736973</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3507906672806824</v>
+        <v>0.3129067940275872</v>
       </c>
       <c r="G65" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4256908000985762</v>
+        <v>0.2687209513841501</v>
       </c>
       <c r="I65" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3766863794258007</v>
+        <v>0.3227430229605531</v>
       </c>
       <c r="K65" t="n">
         <v>1.973210785383696</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4009178912533721</v>
+        <v>0.2625101234736973</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>1.973210785383696</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3507906672806824</v>
+        <v>0.3129067940275872</v>
       </c>
       <c r="G66" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4256908000985762</v>
+        <v>0.2687209513841501</v>
       </c>
       <c r="I66" t="n">
         <v>1.973210785383696</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3766863794258007</v>
+        <v>0.3227430229605531</v>
       </c>
       <c r="K66" t="n">
         <v>1.973210785383696</v>
